--- a/data/output/monthly_report_2026_02.xlsx
+++ b/data/output/monthly_report_2026_02.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Απουσίες" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ημέρες Εργασίας" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Υπερωρίες Αναλυτικά" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Υπερωρίες Σύνολα" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ημέρες" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Υπερωρίες" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Σύνολο Υπερωρίας" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Άδειες" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49,8 +50,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,16 +418,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -463,7 +457,7 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -491,26 +485,26 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>036497310</t>
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ΑΘΑΝΑΣΟΠΟΥΛΟΣ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ΣΤΑΥΡΟΣ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>09/02/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -521,26 +515,26 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>036497310</t>
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ΑΘΑΝΑΣΟΠΟΥΛΟΣ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ΣΤΑΥΡΟΣ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -551,26 +545,26 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>037843072</t>
+        <v>0</v>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ΒΑΒΑΡΟΥΤΑ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ΚΩΝΣΤΑΝΤΙΝΑ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>09/02/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -581,26 +575,26 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>127063376</t>
+        <v>0</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ΞΟΥΛΟΣ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ΓΕΩΡΓΙΟΣ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -611,26 +605,26 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>141897793</t>
+        <v>0</v>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ΔΙΔΑΧΟΥ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ΑΦΡΟΔΙΤΗ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -641,26 +635,26 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>141897793</t>
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ΔΙΔΑΧΟΥ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ΑΦΡΟΔΙΤΗ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>09/02/2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -671,26 +665,26 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>141897793</t>
+        <v>0</v>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ΔΙΔΑΧΟΥ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ΑΦΡΟΔΙΤΗ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -701,26 +695,26 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>157133714</t>
+        <v>0</v>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ΚΑΝΕΛΛΑΚΗΣ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ΚΩΝΣΤΑΝΤΙΝΟΣ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -731,26 +725,26 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>157133714</t>
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ΚΑΝΕΛΛΑΚΗΣ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ΚΩΝΣΤΑΝΤΙΝΟΣ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -761,26 +755,26 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>160088100</t>
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ΔΙΔΑΧΟΣ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ΠΑΝΑΓΙΩΤΗΣ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -791,26 +785,26 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>170907466</t>
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ΔΙΔΑΧΟΣ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ΓΕΩΡΓΙΟΣ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -821,26 +815,26 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>170907466</t>
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ΔΙΔΑΧΟΣ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ΓΕΩΡΓΙΟΣ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -851,26 +845,26 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>170907466</t>
+        <v>0</v>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ΔΙΔΑΧΟΣ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ΓΕΩΡΓΙΟΣ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>18/02/2026</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -881,26 +875,26 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>170907466</t>
+        <v>0</v>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ΔΙΔΑΧΟΣ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ΓΕΩΡΓΙΟΣ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -911,26 +905,26 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>170907466</t>
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ΔΙΔΑΧΟΣ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ΓΕΩΡΓΙΟΣ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -941,26 +935,26 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>170907466</t>
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ΔΙΔΑΧΟΣ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ΓΕΩΡΓΙΟΣ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -971,26 +965,26 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>170907466</t>
+        <v>0</v>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ΔΙΔΑΧΟΣ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ΓΕΩΡΓΙΟΣ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1001,26 +995,26 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>170907466</t>
+        <v>0</v>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ΔΙΔΑΧΟΣ</t>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ΓΕΩΡΓΙΟΣ</t>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1031,29 +1025,1079 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>036497310</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ΑΘΑΝΑΣΟΠΟΥΛΟΣ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ΣΤΑΥΡΟΣ</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>036497310</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ΑΘΑΝΑΣΟΠΟΥΛΟΣ</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ΣΤΑΥΡΟΣ</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>26/02/2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>037843072</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ΒΑΒΑΡΟΥΤΑ</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ΚΩΝΣΤΑΝΤΙΝΑ</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>127063376</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ΞΟΥΛΟΣ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>157133714</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ΚΑΝΕΛΛΑΚΗΣ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ΚΩΝΣΤΑΝΤΙΝΟΣ</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>157133714</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ΚΑΝΕΛΛΑΚΗΣ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ΚΩΝΣΤΑΝΤΙΝΟΣ</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>160088100</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ΔΙΔΑΧΟΣ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ΠΑΝΑΓΙΩΤΗΣ</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>26/02/2026</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
         <is>
           <t>170907466</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>ΔΙΔΑΧΟΣ</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>ΓΕΩΡΓΙΟΣ</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>11/02/2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>170907466</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ΔΙΔΑΧΟΣ</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>170907466</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ΔΙΔΑΧΟΣ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>170907466</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ΔΙΔΑΧΟΣ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>170907466</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ΔΙΔΑΧΟΣ</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>170907466</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ΔΙΔΑΧΟΣ</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>170907466</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ΔΙΔΑΧΟΣ</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>170907466</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ΔΙΔΑΧΟΣ</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>170907466</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ΔΙΔΑΧΟΣ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>27/02/2026</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>11/02/2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>12/02/2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>26/02/2026</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ΑΠΩΝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>ΑΠΩΝ</t>
         </is>
@@ -1072,13 +2116,6 @@
   </sheetPr>
   <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1111,7 +2148,7 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -1134,7 +2171,7 @@
       <c r="A3" t="n">
         <v>0</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -1157,7 +2194,7 @@
       <c r="A4" t="n">
         <v>0</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -1180,7 +2217,7 @@
       <c r="A5" t="n">
         <v>0</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -1203,7 +2240,7 @@
       <c r="A6" t="n">
         <v>0</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -1226,7 +2263,7 @@
       <c r="A7" t="n">
         <v>0</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -1249,7 +2286,7 @@
       <c r="A8" t="n">
         <v>1</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -1272,7 +2309,7 @@
       <c r="A9" t="n">
         <v>1</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -1295,7 +2332,7 @@
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -1318,7 +2355,7 @@
       <c r="A11" t="n">
         <v>1</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -1341,7 +2378,7 @@
       <c r="A12" t="n">
         <v>1</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -1364,7 +2401,7 @@
       <c r="A13" t="n">
         <v>1</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -1387,7 +2424,7 @@
       <c r="A14" t="n">
         <v>1</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -1410,7 +2447,7 @@
       <c r="A15" t="n">
         <v>1</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -1433,7 +2470,7 @@
       <c r="A16" t="n">
         <v>1</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -1456,7 +2493,7 @@
       <c r="A17" t="n">
         <v>1</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -1479,7 +2516,7 @@
       <c r="A18" t="n">
         <v>1</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -1502,7 +2539,7 @@
       <c r="A19" t="n">
         <v>1</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>170907466</t>
         </is>
@@ -1525,7 +2562,7 @@
       <c r="A20" t="n">
         <v>1</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -1557,19 +2594,6 @@
   </sheetPr>
   <dimension ref="A1:K342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1614,7 +2638,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Κατάσταση</t>
+          <t>Υπερωρία</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -1632,7 +2656,7 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -1669,7 +2693,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1685,7 +2709,7 @@
       <c r="A3" t="n">
         <v>0</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -1734,7 +2758,7 @@
       <c r="A4" t="n">
         <v>0</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -1783,7 +2807,7 @@
       <c r="A5" t="n">
         <v>0</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -1832,7 +2856,7 @@
       <c r="A6" t="n">
         <v>0</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -1869,7 +2893,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1885,7 +2909,7 @@
       <c r="A7" t="n">
         <v>0</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -1922,7 +2946,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1938,7 +2962,7 @@
       <c r="A8" t="n">
         <v>0</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -1987,7 +3011,7 @@
       <c r="A9" t="n">
         <v>0</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -2036,7 +3060,7 @@
       <c r="A10" t="n">
         <v>0</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -2085,7 +3109,7 @@
       <c r="A11" t="n">
         <v>0</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -2122,7 +3146,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -2138,7 +3162,7 @@
       <c r="A12" t="n">
         <v>0</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -2187,7 +3211,7 @@
       <c r="A13" t="n">
         <v>0</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -2236,7 +3260,7 @@
       <c r="A14" t="n">
         <v>0</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -2273,7 +3297,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -2289,7 +3313,7 @@
       <c r="A15" t="n">
         <v>0</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -2326,7 +3350,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -2342,7 +3366,7 @@
       <c r="A16" t="n">
         <v>0</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -2391,7 +3415,7 @@
       <c r="A17" t="n">
         <v>0</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -2440,7 +3464,7 @@
       <c r="A18" t="n">
         <v>0</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -2489,7 +3513,7 @@
       <c r="A19" t="n">
         <v>0</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -2526,7 +3550,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -2542,7 +3566,7 @@
       <c r="A20" t="n">
         <v>0</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -2579,7 +3603,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -2595,7 +3619,7 @@
       <c r="A21" t="n">
         <v>0</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -2644,7 +3668,7 @@
       <c r="A22" t="n">
         <v>0</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -2693,7 +3717,7 @@
       <c r="A23" t="n">
         <v>0</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -2742,7 +3766,7 @@
       <c r="A24" t="n">
         <v>0</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -2779,7 +3803,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2795,7 +3819,7 @@
       <c r="A25" t="n">
         <v>0</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -2832,7 +3856,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -2848,7 +3872,7 @@
       <c r="A26" t="n">
         <v>0</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -2897,7 +3921,7 @@
       <c r="A27" t="n">
         <v>0</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -2946,7 +3970,7 @@
       <c r="A28" t="n">
         <v>0</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -2995,7 +4019,7 @@
       <c r="A29" t="n">
         <v>0</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -3032,7 +4056,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -3048,7 +4072,7 @@
       <c r="A30" t="n">
         <v>0</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -3097,7 +4121,7 @@
       <c r="A31" t="n">
         <v>0</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -3146,7 +4170,7 @@
       <c r="A32" t="n">
         <v>0</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -3183,7 +4207,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -3199,7 +4223,7 @@
       <c r="A33" t="n">
         <v>0</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -3236,7 +4260,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -3252,7 +4276,7 @@
       <c r="A34" t="n">
         <v>0</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -3301,7 +4325,7 @@
       <c r="A35" t="n">
         <v>0</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -3338,7 +4362,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -3354,7 +4378,7 @@
       <c r="A36" t="n">
         <v>0</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -3403,7 +4427,7 @@
       <c r="A37" t="n">
         <v>0</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -3452,7 +4476,7 @@
       <c r="A38" t="n">
         <v>0</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -3489,7 +4513,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -3505,7 +4529,7 @@
       <c r="A39" t="n">
         <v>0</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -3542,7 +4566,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -3558,7 +4582,7 @@
       <c r="A40" t="n">
         <v>0</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -3607,7 +4631,7 @@
       <c r="A41" t="n">
         <v>0</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -3656,7 +4680,7 @@
       <c r="A42" t="n">
         <v>0</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -3705,7 +4729,7 @@
       <c r="A43" t="n">
         <v>0</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -3742,7 +4766,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -3758,7 +4782,7 @@
       <c r="A44" t="n">
         <v>0</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -3795,7 +4819,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -3811,7 +4835,7 @@
       <c r="A45" t="n">
         <v>0</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -3860,7 +4884,7 @@
       <c r="A46" t="n">
         <v>0</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -3897,7 +4921,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -3913,7 +4937,7 @@
       <c r="A47" t="n">
         <v>0</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -3962,7 +4986,7 @@
       <c r="A48" t="n">
         <v>0</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -3999,7 +5023,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -4015,7 +5039,7 @@
       <c r="A49" t="n">
         <v>0</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -4064,7 +5088,7 @@
       <c r="A50" t="n">
         <v>0</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -4101,7 +5125,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -4117,7 +5141,7 @@
       <c r="A51" t="n">
         <v>0</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -4154,7 +5178,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -4170,7 +5194,7 @@
       <c r="A52" t="n">
         <v>0</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -4219,7 +5243,7 @@
       <c r="A53" t="n">
         <v>0</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -4268,7 +5292,7 @@
       <c r="A54" t="n">
         <v>0</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -4305,7 +5329,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -4321,7 +5345,7 @@
       <c r="A55" t="n">
         <v>0</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -4370,7 +5394,7 @@
       <c r="A56" t="n">
         <v>0</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -4419,7 +5443,7 @@
       <c r="A57" t="n">
         <v>0</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -4456,7 +5480,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -4472,7 +5496,7 @@
       <c r="A58" t="n">
         <v>0</v>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -4509,7 +5533,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -4525,7 +5549,7 @@
       <c r="A59" t="n">
         <v>0</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -4574,7 +5598,7 @@
       <c r="A60" t="n">
         <v>0</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -4623,7 +5647,7 @@
       <c r="A61" t="n">
         <v>0</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -4672,7 +5696,7 @@
       <c r="A62" t="n">
         <v>0</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -4709,7 +5733,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -4725,7 +5749,7 @@
       <c r="A63" t="n">
         <v>0</v>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -4762,7 +5786,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -4778,7 +5802,7 @@
       <c r="A64" t="n">
         <v>0</v>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -4827,7 +5851,7 @@
       <c r="A65" t="n">
         <v>0</v>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -4864,7 +5888,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -4880,7 +5904,7 @@
       <c r="A66" t="n">
         <v>0</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -4929,7 +5953,7 @@
       <c r="A67" t="n">
         <v>0</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -4966,7 +5990,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -4982,7 +6006,7 @@
       <c r="A68" t="n">
         <v>0</v>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -5031,7 +6055,7 @@
       <c r="A69" t="n">
         <v>0</v>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -5068,7 +6092,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -5084,7 +6108,7 @@
       <c r="A70" t="n">
         <v>0</v>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -5121,7 +6145,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -5137,7 +6161,7 @@
       <c r="A71" t="n">
         <v>0</v>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -5186,7 +6210,7 @@
       <c r="A72" t="n">
         <v>0</v>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -5235,7 +6259,7 @@
       <c r="A73" t="n">
         <v>0</v>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -5272,7 +6296,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -5288,7 +6312,7 @@
       <c r="A74" t="n">
         <v>0</v>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -5337,7 +6361,7 @@
       <c r="A75" t="n">
         <v>0</v>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -5386,7 +6410,7 @@
       <c r="A76" t="n">
         <v>0</v>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -5435,7 +6459,7 @@
       <c r="A77" t="n">
         <v>0</v>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -5472,7 +6496,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -5488,7 +6512,7 @@
       <c r="A78" t="n">
         <v>0</v>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -5537,7 +6561,7 @@
       <c r="A79" t="n">
         <v>0</v>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -5586,7 +6610,7 @@
       <c r="A80" t="n">
         <v>0</v>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -5635,7 +6659,7 @@
       <c r="A81" t="n">
         <v>0</v>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -5672,7 +6696,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -5688,7 +6712,7 @@
       <c r="A82" t="n">
         <v>0</v>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -5725,7 +6749,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -5741,7 +6765,7 @@
       <c r="A83" t="n">
         <v>0</v>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -5790,7 +6814,7 @@
       <c r="A84" t="n">
         <v>0</v>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -5839,7 +6863,7 @@
       <c r="A85" t="n">
         <v>0</v>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -5888,7 +6912,7 @@
       <c r="A86" t="n">
         <v>0</v>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -5925,7 +6949,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -5941,7 +6965,7 @@
       <c r="A87" t="n">
         <v>0</v>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -5990,7 +7014,7 @@
       <c r="A88" t="n">
         <v>0</v>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -6039,7 +7063,7 @@
       <c r="A89" t="n">
         <v>0</v>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -6076,7 +7100,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -6092,7 +7116,7 @@
       <c r="A90" t="n">
         <v>0</v>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -6141,7 +7165,7 @@
       <c r="A91" t="n">
         <v>0</v>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -6190,7 +7214,7 @@
       <c r="A92" t="n">
         <v>0</v>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -6227,7 +7251,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -6243,7 +7267,7 @@
       <c r="A93" t="n">
         <v>0</v>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -6292,7 +7316,7 @@
       <c r="A94" t="n">
         <v>0</v>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -6341,7 +7365,7 @@
       <c r="A95" t="n">
         <v>0</v>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -6378,7 +7402,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -6394,7 +7418,7 @@
       <c r="A96" t="n">
         <v>0</v>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -6431,7 +7455,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -6447,7 +7471,7 @@
       <c r="A97" t="n">
         <v>0</v>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -6496,7 +7520,7 @@
       <c r="A98" t="n">
         <v>0</v>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -6545,7 +7569,7 @@
       <c r="A99" t="n">
         <v>0</v>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -6594,7 +7618,7 @@
       <c r="A100" t="n">
         <v>0</v>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -6631,7 +7655,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -6647,7 +7671,7 @@
       <c r="A101" t="n">
         <v>0</v>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -6684,7 +7708,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -6700,7 +7724,7 @@
       <c r="A102" t="n">
         <v>0</v>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -6749,7 +7773,7 @@
       <c r="A103" t="n">
         <v>0</v>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -6798,7 +7822,7 @@
       <c r="A104" t="n">
         <v>0</v>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -6847,7 +7871,7 @@
       <c r="A105" t="n">
         <v>0</v>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -6884,7 +7908,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -6900,7 +7924,7 @@
       <c r="A106" t="n">
         <v>0</v>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -6949,7 +7973,7 @@
       <c r="A107" t="n">
         <v>0</v>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -6998,7 +8022,7 @@
       <c r="A108" t="n">
         <v>0</v>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -7035,7 +8059,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -7051,7 +8075,7 @@
       <c r="A109" t="n">
         <v>0</v>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -7088,7 +8112,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -7104,7 +8128,7 @@
       <c r="A110" t="n">
         <v>0</v>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -7153,7 +8177,7 @@
       <c r="A111" t="n">
         <v>0</v>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -7190,7 +8214,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -7206,7 +8230,7 @@
       <c r="A112" t="n">
         <v>0</v>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -7255,7 +8279,7 @@
       <c r="A113" t="n">
         <v>0</v>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -7304,7 +8328,7 @@
       <c r="A114" t="n">
         <v>0</v>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -7341,7 +8365,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -7357,7 +8381,7 @@
       <c r="A115" t="n">
         <v>1</v>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -7394,7 +8418,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -7410,7 +8434,7 @@
       <c r="A116" t="n">
         <v>1</v>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -7447,7 +8471,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -7463,7 +8487,7 @@
       <c r="A117" t="n">
         <v>1</v>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -7500,7 +8524,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -7516,7 +8540,7 @@
       <c r="A118" t="n">
         <v>1</v>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -7553,7 +8577,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -7569,7 +8593,7 @@
       <c r="A119" t="n">
         <v>1</v>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -7606,7 +8630,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -7622,7 +8646,7 @@
       <c r="A120" t="n">
         <v>1</v>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -7659,7 +8683,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -7675,7 +8699,7 @@
       <c r="A121" t="n">
         <v>1</v>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -7724,7 +8748,7 @@
       <c r="A122" t="n">
         <v>1</v>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -7773,7 +8797,7 @@
       <c r="A123" t="n">
         <v>1</v>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -7810,7 +8834,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -7826,7 +8850,7 @@
       <c r="A124" t="n">
         <v>1</v>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -7863,7 +8887,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -7879,7 +8903,7 @@
       <c r="A125" t="n">
         <v>1</v>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -7928,7 +8952,7 @@
       <c r="A126" t="n">
         <v>1</v>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -7965,7 +8989,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -7981,7 +9005,7 @@
       <c r="A127" t="n">
         <v>1</v>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B127" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -8030,7 +9054,7 @@
       <c r="A128" t="n">
         <v>1</v>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -8079,7 +9103,7 @@
       <c r="A129" t="n">
         <v>1</v>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B129" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -8128,7 +9152,7 @@
       <c r="A130" t="n">
         <v>1</v>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B130" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -8177,7 +9201,7 @@
       <c r="A131" t="n">
         <v>1</v>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B131" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -8214,7 +9238,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -8230,7 +9254,7 @@
       <c r="A132" t="n">
         <v>1</v>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B132" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -8267,7 +9291,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -8283,7 +9307,7 @@
       <c r="A133" t="n">
         <v>1</v>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B133" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -8320,7 +9344,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -8336,7 +9360,7 @@
       <c r="A134" t="n">
         <v>1</v>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B134" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -8373,7 +9397,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -8389,7 +9413,7 @@
       <c r="A135" t="n">
         <v>1</v>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B135" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -8426,7 +9450,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -8442,7 +9466,7 @@
       <c r="A136" t="n">
         <v>1</v>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B136" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -8479,7 +9503,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -8495,7 +9519,7 @@
       <c r="A137" t="n">
         <v>1</v>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B137" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -8532,7 +9556,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -8548,7 +9572,7 @@
       <c r="A138" t="n">
         <v>1</v>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B138" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -8597,7 +9621,7 @@
       <c r="A139" t="n">
         <v>1</v>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B139" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -8646,7 +9670,7 @@
       <c r="A140" t="n">
         <v>1</v>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B140" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -8695,7 +9719,7 @@
       <c r="A141" t="n">
         <v>1</v>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B141" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -8744,7 +9768,7 @@
       <c r="A142" t="n">
         <v>1</v>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B142" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -8781,7 +9805,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -8797,7 +9821,7 @@
       <c r="A143" t="n">
         <v>1</v>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B143" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -8834,7 +9858,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -8850,7 +9874,7 @@
       <c r="A144" t="n">
         <v>1</v>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B144" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -8899,7 +9923,7 @@
       <c r="A145" t="n">
         <v>1</v>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B145" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -8948,7 +9972,7 @@
       <c r="A146" t="n">
         <v>1</v>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B146" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -8997,7 +10021,7 @@
       <c r="A147" t="n">
         <v>1</v>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B147" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -9046,7 +10070,7 @@
       <c r="A148" t="n">
         <v>1</v>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B148" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -9095,7 +10119,7 @@
       <c r="A149" t="n">
         <v>1</v>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B149" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -9144,7 +10168,7 @@
       <c r="A150" t="n">
         <v>1</v>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B150" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -9181,7 +10205,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -9197,7 +10221,7 @@
       <c r="A151" t="n">
         <v>1</v>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B151" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -9234,7 +10258,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -9250,7 +10274,7 @@
       <c r="A152" t="n">
         <v>1</v>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B152" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -9299,7 +10323,7 @@
       <c r="A153" t="n">
         <v>1</v>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B153" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -9336,7 +10360,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -9352,7 +10376,7 @@
       <c r="A154" t="n">
         <v>1</v>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B154" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -9389,7 +10413,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -9405,7 +10429,7 @@
       <c r="A155" t="n">
         <v>1</v>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B155" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -9442,7 +10466,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -9458,7 +10482,7 @@
       <c r="A156" t="n">
         <v>1</v>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B156" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -9507,7 +10531,7 @@
       <c r="A157" t="n">
         <v>1</v>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B157" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -9544,7 +10568,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -9560,7 +10584,7 @@
       <c r="A158" t="n">
         <v>1</v>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B158" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -9597,7 +10621,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -9613,7 +10637,7 @@
       <c r="A159" t="n">
         <v>1</v>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B159" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -9650,7 +10674,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -9666,7 +10690,7 @@
       <c r="A160" t="n">
         <v>1</v>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B160" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -9715,7 +10739,7 @@
       <c r="A161" t="n">
         <v>1</v>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B161" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -9764,7 +10788,7 @@
       <c r="A162" t="n">
         <v>1</v>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B162" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -9801,7 +10825,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -9817,7 +10841,7 @@
       <c r="A163" t="n">
         <v>1</v>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B163" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -9866,7 +10890,7 @@
       <c r="A164" t="n">
         <v>1</v>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B164" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -9903,7 +10927,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -9919,7 +10943,7 @@
       <c r="A165" t="n">
         <v>1</v>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B165" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -9956,7 +10980,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -9972,7 +10996,7 @@
       <c r="A166" t="n">
         <v>1</v>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B166" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -10021,7 +11045,7 @@
       <c r="A167" t="n">
         <v>1</v>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B167" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -10070,7 +11094,7 @@
       <c r="A168" t="n">
         <v>1</v>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B168" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -10119,7 +11143,7 @@
       <c r="A169" t="n">
         <v>1</v>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B169" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10156,7 +11180,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -10172,7 +11196,7 @@
       <c r="A170" t="n">
         <v>1</v>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B170" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10209,7 +11233,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -10225,7 +11249,7 @@
       <c r="A171" t="n">
         <v>1</v>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B171" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10274,7 +11298,7 @@
       <c r="A172" t="n">
         <v>1</v>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B172" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10311,7 +11335,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J172" t="n">
@@ -10327,7 +11351,7 @@
       <c r="A173" t="n">
         <v>1</v>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B173" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10376,7 +11400,7 @@
       <c r="A174" t="n">
         <v>1</v>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B174" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10413,7 +11437,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -10429,7 +11453,7 @@
       <c r="A175" t="n">
         <v>1</v>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B175" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10466,7 +11490,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -10482,7 +11506,7 @@
       <c r="A176" t="n">
         <v>1</v>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B176" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10519,7 +11543,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J176" t="n">
@@ -10535,7 +11559,7 @@
       <c r="A177" t="n">
         <v>1</v>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B177" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10584,7 +11608,7 @@
       <c r="A178" t="n">
         <v>1</v>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B178" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10633,7 +11657,7 @@
       <c r="A179" t="n">
         <v>1</v>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B179" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10682,7 +11706,7 @@
       <c r="A180" t="n">
         <v>1</v>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B180" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10731,7 +11755,7 @@
       <c r="A181" t="n">
         <v>1</v>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B181" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10768,7 +11792,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J181" t="n">
@@ -10784,7 +11808,7 @@
       <c r="A182" t="n">
         <v>1</v>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B182" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10833,7 +11857,7 @@
       <c r="A183" t="n">
         <v>1</v>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B183" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10882,7 +11906,7 @@
       <c r="A184" t="n">
         <v>1</v>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B184" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10931,7 +11955,7 @@
       <c r="A185" t="n">
         <v>1</v>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B185" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -10980,7 +12004,7 @@
       <c r="A186" t="n">
         <v>1</v>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B186" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -11029,7 +12053,7 @@
       <c r="A187" t="n">
         <v>1</v>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B187" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -11066,7 +12090,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J187" t="n">
@@ -11082,7 +12106,7 @@
       <c r="A188" t="n">
         <v>1</v>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B188" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11119,7 +12143,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J188" t="n">
@@ -11135,7 +12159,7 @@
       <c r="A189" t="n">
         <v>1</v>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="B189" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11172,7 +12196,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J189" t="n">
@@ -11188,7 +12212,7 @@
       <c r="A190" t="n">
         <v>1</v>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B190" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11225,7 +12249,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J190" t="n">
@@ -11241,7 +12265,7 @@
       <c r="A191" t="n">
         <v>1</v>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B191" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11278,7 +12302,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J191" t="n">
@@ -11294,7 +12318,7 @@
       <c r="A192" t="n">
         <v>1</v>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B192" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11331,7 +12355,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J192" t="n">
@@ -11347,7 +12371,7 @@
       <c r="A193" t="n">
         <v>1</v>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B193" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11384,7 +12408,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J193" t="n">
@@ -11400,7 +12424,7 @@
       <c r="A194" t="n">
         <v>1</v>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B194" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11449,7 +12473,7 @@
       <c r="A195" t="n">
         <v>1</v>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B195" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11498,7 +12522,7 @@
       <c r="A196" t="n">
         <v>1</v>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="B196" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11547,7 +12571,7 @@
       <c r="A197" t="n">
         <v>1</v>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B197" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11596,7 +12620,7 @@
       <c r="A198" t="n">
         <v>1</v>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B198" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11645,7 +12669,7 @@
       <c r="A199" t="n">
         <v>1</v>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B199" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11682,7 +12706,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J199" t="n">
@@ -11698,7 +12722,7 @@
       <c r="A200" t="n">
         <v>1</v>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="B200" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11735,7 +12759,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J200" t="n">
@@ -11751,7 +12775,7 @@
       <c r="A201" t="n">
         <v>1</v>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B201" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11800,7 +12824,7 @@
       <c r="A202" t="n">
         <v>1</v>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="B202" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11849,7 +12873,7 @@
       <c r="A203" t="n">
         <v>1</v>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B203" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11898,7 +12922,7 @@
       <c r="A204" t="n">
         <v>1</v>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B204" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11947,7 +12971,7 @@
       <c r="A205" t="n">
         <v>1</v>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B205" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -11996,7 +13020,7 @@
       <c r="A206" t="n">
         <v>1</v>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B206" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -12045,7 +13069,7 @@
       <c r="A207" t="n">
         <v>1</v>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B207" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12082,7 +13106,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J207" t="n">
@@ -12098,7 +13122,7 @@
       <c r="A208" t="n">
         <v>1</v>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B208" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12147,7 +13171,7 @@
       <c r="A209" t="n">
         <v>1</v>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B209" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12184,7 +13208,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J209" t="n">
@@ -12200,7 +13224,7 @@
       <c r="A210" t="n">
         <v>1</v>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B210" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12237,7 +13261,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J210" t="n">
@@ -12253,7 +13277,7 @@
       <c r="A211" t="n">
         <v>1</v>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B211" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12302,7 +13326,7 @@
       <c r="A212" t="n">
         <v>1</v>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B212" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12339,7 +13363,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J212" t="n">
@@ -12355,7 +13379,7 @@
       <c r="A213" t="n">
         <v>1</v>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B213" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12404,7 +13428,7 @@
       <c r="A214" t="n">
         <v>1</v>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B214" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12453,7 +13477,7 @@
       <c r="A215" t="n">
         <v>1</v>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B215" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12490,7 +13514,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J215" t="n">
@@ -12506,7 +13530,7 @@
       <c r="A216" t="n">
         <v>1</v>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B216" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12543,7 +13567,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J216" t="n">
@@ -12559,7 +13583,7 @@
       <c r="A217" t="n">
         <v>1</v>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B217" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12596,7 +13620,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J217" t="n">
@@ -12612,7 +13636,7 @@
       <c r="A218" t="n">
         <v>1</v>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B218" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12649,7 +13673,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J218" t="n">
@@ -12665,7 +13689,7 @@
       <c r="A219" t="n">
         <v>1</v>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B219" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12714,7 +13738,7 @@
       <c r="A220" t="n">
         <v>1</v>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B220" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12763,7 +13787,7 @@
       <c r="A221" t="n">
         <v>1</v>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B221" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12812,7 +13836,7 @@
       <c r="A222" t="n">
         <v>1</v>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B222" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12861,7 +13885,7 @@
       <c r="A223" t="n">
         <v>1</v>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B223" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12910,7 +13934,7 @@
       <c r="A224" t="n">
         <v>1</v>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B224" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -12947,7 +13971,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J224" t="n">
@@ -12963,7 +13987,7 @@
       <c r="A225" t="n">
         <v>1</v>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B225" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -13012,7 +14036,7 @@
       <c r="A226" t="n">
         <v>1</v>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B226" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -13061,7 +14085,7 @@
       <c r="A227" t="n">
         <v>1</v>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B227" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -13110,7 +14134,7 @@
       <c r="A228" t="n">
         <v>1</v>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B228" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -13159,7 +14183,7 @@
       <c r="A229" t="n">
         <v>1</v>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B229" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -13208,7 +14232,7 @@
       <c r="A230" t="n">
         <v>1</v>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B230" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -13257,7 +14281,7 @@
       <c r="A231" t="n">
         <v>1</v>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B231" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -13294,7 +14318,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J231" t="n">
@@ -13310,7 +14334,7 @@
       <c r="A232" t="n">
         <v>1</v>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B232" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -13359,7 +14383,7 @@
       <c r="A233" t="n">
         <v>1</v>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B233" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -13396,7 +14420,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J233" t="n">
@@ -13412,7 +14436,7 @@
       <c r="A234" t="n">
         <v>1</v>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B234" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -13449,7 +14473,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J234" t="n">
@@ -13465,7 +14489,7 @@
       <c r="A235" t="n">
         <v>1</v>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B235" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -13514,7 +14538,7 @@
       <c r="A236" t="n">
         <v>1</v>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B236" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -13563,7 +14587,7 @@
       <c r="A237" t="n">
         <v>1</v>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B237" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -13612,7 +14636,7 @@
       <c r="A238" t="n">
         <v>1</v>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B238" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -13661,7 +14685,7 @@
       <c r="A239" t="n">
         <v>1</v>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B239" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -13710,7 +14734,7 @@
       <c r="A240" t="n">
         <v>1</v>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B240" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -13759,7 +14783,7 @@
       <c r="A241" t="n">
         <v>1</v>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B241" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -13796,7 +14820,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J241" t="n">
@@ -13812,7 +14836,7 @@
       <c r="A242" t="n">
         <v>1</v>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B242" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -13849,7 +14873,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J242" t="n">
@@ -13865,7 +14889,7 @@
       <c r="A243" t="n">
         <v>1</v>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B243" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -13902,7 +14926,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J243" t="n">
@@ -13918,7 +14942,7 @@
       <c r="A244" t="n">
         <v>1</v>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B244" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -13955,7 +14979,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J244" t="n">
@@ -13971,7 +14995,7 @@
       <c r="A245" t="n">
         <v>1</v>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B245" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -14008,7 +15032,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J245" t="n">
@@ -14024,7 +15048,7 @@
       <c r="A246" t="n">
         <v>1</v>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="B246" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -14061,7 +15085,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J246" t="n">
@@ -14077,7 +15101,7 @@
       <c r="A247" t="n">
         <v>1</v>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B247" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -14114,7 +15138,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J247" t="n">
@@ -14130,7 +15154,7 @@
       <c r="A248" t="n">
         <v>1</v>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="B248" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -14179,7 +15203,7 @@
       <c r="A249" t="n">
         <v>1</v>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B249" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -14228,7 +15252,7 @@
       <c r="A250" t="n">
         <v>1</v>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B250" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -14265,7 +15289,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J250" t="n">
@@ -14281,7 +15305,7 @@
       <c r="A251" t="n">
         <v>1</v>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B251" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -14318,7 +15342,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J251" t="n">
@@ -14334,7 +15358,7 @@
       <c r="A252" t="n">
         <v>1</v>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B252" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -14371,7 +15395,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J252" t="n">
@@ -14387,7 +15411,7 @@
       <c r="A253" t="n">
         <v>1</v>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B253" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -14424,7 +15448,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J253" t="n">
@@ -14440,7 +15464,7 @@
       <c r="A254" t="n">
         <v>1</v>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B254" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -14489,7 +15513,7 @@
       <c r="A255" t="n">
         <v>1</v>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B255" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -14538,7 +15562,7 @@
       <c r="A256" t="n">
         <v>1</v>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B256" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -14587,7 +15611,7 @@
       <c r="A257" t="n">
         <v>1</v>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B257" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -14636,7 +15660,7 @@
       <c r="A258" t="n">
         <v>1</v>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B258" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -14685,7 +15709,7 @@
       <c r="A259" t="n">
         <v>1</v>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B259" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -14734,7 +15758,7 @@
       <c r="A260" t="n">
         <v>1</v>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B260" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -14771,7 +15795,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J260" t="n">
@@ -14787,7 +15811,7 @@
       <c r="A261" t="n">
         <v>1</v>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B261" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -14824,7 +15848,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J261" t="n">
@@ -14840,7 +15864,7 @@
       <c r="A262" t="n">
         <v>1</v>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B262" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -14877,7 +15901,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J262" t="n">
@@ -14893,7 +15917,7 @@
       <c r="A263" t="n">
         <v>1</v>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B263" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -14930,7 +15954,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J263" t="n">
@@ -14946,7 +15970,7 @@
       <c r="A264" t="n">
         <v>1</v>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B264" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -14983,7 +16007,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J264" t="n">
@@ -14999,7 +16023,7 @@
       <c r="A265" t="n">
         <v>1</v>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B265" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -15036,7 +16060,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J265" t="n">
@@ -15052,7 +16076,7 @@
       <c r="A266" t="n">
         <v>1</v>
       </c>
-      <c r="B266" t="inlineStr">
+      <c r="B266" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -15089,7 +16113,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J266" t="n">
@@ -15105,7 +16129,7 @@
       <c r="A267" t="n">
         <v>1</v>
       </c>
-      <c r="B267" t="inlineStr">
+      <c r="B267" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -15142,7 +16166,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J267" t="n">
@@ -15158,7 +16182,7 @@
       <c r="A268" t="n">
         <v>1</v>
       </c>
-      <c r="B268" t="inlineStr">
+      <c r="B268" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -15207,7 +16231,7 @@
       <c r="A269" t="n">
         <v>1</v>
       </c>
-      <c r="B269" t="inlineStr">
+      <c r="B269" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -15244,7 +16268,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J269" t="n">
@@ -15260,7 +16284,7 @@
       <c r="A270" t="n">
         <v>1</v>
       </c>
-      <c r="B270" t="inlineStr">
+      <c r="B270" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -15297,7 +16321,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J270" t="n">
@@ -15313,7 +16337,7 @@
       <c r="A271" t="n">
         <v>1</v>
       </c>
-      <c r="B271" t="inlineStr">
+      <c r="B271" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -15350,7 +16374,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J271" t="n">
@@ -15366,7 +16390,7 @@
       <c r="A272" t="n">
         <v>1</v>
       </c>
-      <c r="B272" t="inlineStr">
+      <c r="B272" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -15403,7 +16427,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J272" t="n">
@@ -15419,7 +16443,7 @@
       <c r="A273" t="n">
         <v>1</v>
       </c>
-      <c r="B273" t="inlineStr">
+      <c r="B273" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -15468,7 +16492,7 @@
       <c r="A274" t="n">
         <v>1</v>
       </c>
-      <c r="B274" t="inlineStr">
+      <c r="B274" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -15517,7 +16541,7 @@
       <c r="A275" t="n">
         <v>1</v>
       </c>
-      <c r="B275" t="inlineStr">
+      <c r="B275" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -15554,7 +16578,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J275" t="n">
@@ -15570,7 +16594,7 @@
       <c r="A276" t="n">
         <v>1</v>
       </c>
-      <c r="B276" t="inlineStr">
+      <c r="B276" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -15619,7 +16643,7 @@
       <c r="A277" t="n">
         <v>1</v>
       </c>
-      <c r="B277" t="inlineStr">
+      <c r="B277" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -15668,7 +16692,7 @@
       <c r="A278" t="n">
         <v>1</v>
       </c>
-      <c r="B278" t="inlineStr">
+      <c r="B278" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -15717,7 +16741,7 @@
       <c r="A279" t="n">
         <v>1</v>
       </c>
-      <c r="B279" t="inlineStr">
+      <c r="B279" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -15754,7 +16778,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J279" t="n">
@@ -15770,7 +16794,7 @@
       <c r="A280" t="n">
         <v>1</v>
       </c>
-      <c r="B280" t="inlineStr">
+      <c r="B280" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -15807,7 +16831,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J280" t="n">
@@ -15823,7 +16847,7 @@
       <c r="A281" t="n">
         <v>1</v>
       </c>
-      <c r="B281" t="inlineStr">
+      <c r="B281" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -15860,7 +16884,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J281" t="n">
@@ -15876,7 +16900,7 @@
       <c r="A282" t="n">
         <v>1</v>
       </c>
-      <c r="B282" t="inlineStr">
+      <c r="B282" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -15913,7 +16937,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J282" t="n">
@@ -15929,7 +16953,7 @@
       <c r="A283" t="n">
         <v>1</v>
       </c>
-      <c r="B283" t="inlineStr">
+      <c r="B283" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -15978,7 +17002,7 @@
       <c r="A284" t="n">
         <v>1</v>
       </c>
-      <c r="B284" t="inlineStr">
+      <c r="B284" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -16015,7 +17039,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J284" t="n">
@@ -16031,7 +17055,7 @@
       <c r="A285" t="n">
         <v>1</v>
       </c>
-      <c r="B285" t="inlineStr">
+      <c r="B285" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -16080,7 +17104,7 @@
       <c r="A286" t="n">
         <v>1</v>
       </c>
-      <c r="B286" t="inlineStr">
+      <c r="B286" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -16117,7 +17141,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J286" t="n">
@@ -16133,7 +17157,7 @@
       <c r="A287" t="n">
         <v>1</v>
       </c>
-      <c r="B287" t="inlineStr">
+      <c r="B287" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -16170,7 +17194,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J287" t="n">
@@ -16186,7 +17210,7 @@
       <c r="A288" t="n">
         <v>1</v>
       </c>
-      <c r="B288" t="inlineStr">
+      <c r="B288" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -16223,7 +17247,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J288" t="n">
@@ -16239,7 +17263,7 @@
       <c r="A289" t="n">
         <v>1</v>
       </c>
-      <c r="B289" t="inlineStr">
+      <c r="B289" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -16288,7 +17312,7 @@
       <c r="A290" t="n">
         <v>1</v>
       </c>
-      <c r="B290" t="inlineStr">
+      <c r="B290" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -16325,7 +17349,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J290" t="n">
@@ -16341,7 +17365,7 @@
       <c r="A291" t="n">
         <v>1</v>
       </c>
-      <c r="B291" t="inlineStr">
+      <c r="B291" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -16390,7 +17414,7 @@
       <c r="A292" t="n">
         <v>1</v>
       </c>
-      <c r="B292" t="inlineStr">
+      <c r="B292" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -16439,7 +17463,7 @@
       <c r="A293" t="n">
         <v>1</v>
       </c>
-      <c r="B293" t="inlineStr">
+      <c r="B293" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -16488,7 +17512,7 @@
       <c r="A294" t="n">
         <v>1</v>
       </c>
-      <c r="B294" t="inlineStr">
+      <c r="B294" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -16537,7 +17561,7 @@
       <c r="A295" t="n">
         <v>1</v>
       </c>
-      <c r="B295" t="inlineStr">
+      <c r="B295" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -16586,7 +17610,7 @@
       <c r="A296" t="n">
         <v>1</v>
       </c>
-      <c r="B296" t="inlineStr">
+      <c r="B296" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -16623,7 +17647,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J296" t="n">
@@ -16639,7 +17663,7 @@
       <c r="A297" t="n">
         <v>1</v>
       </c>
-      <c r="B297" t="inlineStr">
+      <c r="B297" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -16676,7 +17700,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J297" t="n">
@@ -16692,7 +17716,7 @@
       <c r="A298" t="n">
         <v>1</v>
       </c>
-      <c r="B298" t="inlineStr">
+      <c r="B298" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -16741,7 +17765,7 @@
       <c r="A299" t="n">
         <v>1</v>
       </c>
-      <c r="B299" t="inlineStr">
+      <c r="B299" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -16790,7 +17814,7 @@
       <c r="A300" t="n">
         <v>1</v>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B300" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -16827,7 +17851,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J300" t="n">
@@ -16843,7 +17867,7 @@
       <c r="A301" t="n">
         <v>1</v>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B301" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -16892,7 +17916,7 @@
       <c r="A302" t="n">
         <v>1</v>
       </c>
-      <c r="B302" t="inlineStr">
+      <c r="B302" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -16941,7 +17965,7 @@
       <c r="A303" t="n">
         <v>1</v>
       </c>
-      <c r="B303" t="inlineStr">
+      <c r="B303" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -16990,7 +18014,7 @@
       <c r="A304" t="n">
         <v>1</v>
       </c>
-      <c r="B304" t="inlineStr">
+      <c r="B304" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -17039,7 +18063,7 @@
       <c r="A305" t="n">
         <v>1</v>
       </c>
-      <c r="B305" t="inlineStr">
+      <c r="B305" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -17088,7 +18112,7 @@
       <c r="A306" t="n">
         <v>1</v>
       </c>
-      <c r="B306" t="inlineStr">
+      <c r="B306" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -17137,7 +18161,7 @@
       <c r="A307" t="n">
         <v>1</v>
       </c>
-      <c r="B307" t="inlineStr">
+      <c r="B307" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -17186,7 +18210,7 @@
       <c r="A308" t="n">
         <v>1</v>
       </c>
-      <c r="B308" t="inlineStr">
+      <c r="B308" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -17235,7 +18259,7 @@
       <c r="A309" t="n">
         <v>1</v>
       </c>
-      <c r="B309" t="inlineStr">
+      <c r="B309" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -17284,7 +18308,7 @@
       <c r="A310" t="n">
         <v>1</v>
       </c>
-      <c r="B310" t="inlineStr">
+      <c r="B310" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -17333,7 +18357,7 @@
       <c r="A311" t="n">
         <v>1</v>
       </c>
-      <c r="B311" t="inlineStr">
+      <c r="B311" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -17382,7 +18406,7 @@
       <c r="A312" t="n">
         <v>1</v>
       </c>
-      <c r="B312" t="inlineStr">
+      <c r="B312" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -17431,7 +18455,7 @@
       <c r="A313" t="n">
         <v>1</v>
       </c>
-      <c r="B313" t="inlineStr">
+      <c r="B313" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -17480,7 +18504,7 @@
       <c r="A314" t="n">
         <v>1</v>
       </c>
-      <c r="B314" t="inlineStr">
+      <c r="B314" s="1" t="inlineStr">
         <is>
           <t>170907466</t>
         </is>
@@ -17517,7 +18541,7 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J314" t="n">
@@ -17533,7 +18557,7 @@
       <c r="A315" t="n">
         <v>1</v>
       </c>
-      <c r="B315" t="inlineStr">
+      <c r="B315" s="1" t="inlineStr">
         <is>
           <t>170907466</t>
         </is>
@@ -17582,7 +18606,7 @@
       <c r="A316" t="n">
         <v>1</v>
       </c>
-      <c r="B316" t="inlineStr">
+      <c r="B316" s="1" t="inlineStr">
         <is>
           <t>170907466</t>
         </is>
@@ -17631,7 +18655,7 @@
       <c r="A317" t="n">
         <v>1</v>
       </c>
-      <c r="B317" t="inlineStr">
+      <c r="B317" s="1" t="inlineStr">
         <is>
           <t>170907466</t>
         </is>
@@ -17668,7 +18692,7 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J317" t="n">
@@ -17684,7 +18708,7 @@
       <c r="A318" t="n">
         <v>1</v>
       </c>
-      <c r="B318" t="inlineStr">
+      <c r="B318" s="1" t="inlineStr">
         <is>
           <t>170907466</t>
         </is>
@@ -17721,7 +18745,7 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J318" t="n">
@@ -17737,7 +18761,7 @@
       <c r="A319" t="n">
         <v>1</v>
       </c>
-      <c r="B319" t="inlineStr">
+      <c r="B319" s="1" t="inlineStr">
         <is>
           <t>170907466</t>
         </is>
@@ -17786,7 +18810,7 @@
       <c r="A320" t="n">
         <v>1</v>
       </c>
-      <c r="B320" t="inlineStr">
+      <c r="B320" s="1" t="inlineStr">
         <is>
           <t>170907466</t>
         </is>
@@ -17835,7 +18859,7 @@
       <c r="A321" t="n">
         <v>1</v>
       </c>
-      <c r="B321" t="inlineStr">
+      <c r="B321" s="1" t="inlineStr">
         <is>
           <t>170907466</t>
         </is>
@@ -17884,7 +18908,7 @@
       <c r="A322" t="n">
         <v>1</v>
       </c>
-      <c r="B322" t="inlineStr">
+      <c r="B322" s="1" t="inlineStr">
         <is>
           <t>170907466</t>
         </is>
@@ -17933,7 +18957,7 @@
       <c r="A323" t="n">
         <v>1</v>
       </c>
-      <c r="B323" t="inlineStr">
+      <c r="B323" s="1" t="inlineStr">
         <is>
           <t>170907466</t>
         </is>
@@ -17982,7 +19006,7 @@
       <c r="A324" t="n">
         <v>1</v>
       </c>
-      <c r="B324" t="inlineStr">
+      <c r="B324" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18019,7 +19043,7 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J324" t="n">
@@ -18035,7 +19059,7 @@
       <c r="A325" t="n">
         <v>1</v>
       </c>
-      <c r="B325" t="inlineStr">
+      <c r="B325" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18072,7 +19096,7 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J325" t="n">
@@ -18088,7 +19112,7 @@
       <c r="A326" t="n">
         <v>1</v>
       </c>
-      <c r="B326" t="inlineStr">
+      <c r="B326" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18137,7 +19161,7 @@
       <c r="A327" t="n">
         <v>1</v>
       </c>
-      <c r="B327" t="inlineStr">
+      <c r="B327" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18174,7 +19198,7 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J327" t="n">
@@ -18190,7 +19214,7 @@
       <c r="A328" t="n">
         <v>1</v>
       </c>
-      <c r="B328" t="inlineStr">
+      <c r="B328" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18227,7 +19251,7 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J328" t="n">
@@ -18243,7 +19267,7 @@
       <c r="A329" t="n">
         <v>1</v>
       </c>
-      <c r="B329" t="inlineStr">
+      <c r="B329" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18292,7 +19316,7 @@
       <c r="A330" t="n">
         <v>1</v>
       </c>
-      <c r="B330" t="inlineStr">
+      <c r="B330" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18341,7 +19365,7 @@
       <c r="A331" t="n">
         <v>1</v>
       </c>
-      <c r="B331" t="inlineStr">
+      <c r="B331" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18378,7 +19402,7 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J331" t="n">
@@ -18394,7 +19418,7 @@
       <c r="A332" t="n">
         <v>1</v>
       </c>
-      <c r="B332" t="inlineStr">
+      <c r="B332" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18443,7 +19467,7 @@
       <c r="A333" t="n">
         <v>1</v>
       </c>
-      <c r="B333" t="inlineStr">
+      <c r="B333" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18480,7 +19504,7 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J333" t="n">
@@ -18496,7 +19520,7 @@
       <c r="A334" t="n">
         <v>1</v>
       </c>
-      <c r="B334" t="inlineStr">
+      <c r="B334" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18533,7 +19557,7 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J334" t="n">
@@ -18549,7 +19573,7 @@
       <c r="A335" t="n">
         <v>1</v>
       </c>
-      <c r="B335" t="inlineStr">
+      <c r="B335" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18586,7 +19610,7 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J335" t="n">
@@ -18602,7 +19626,7 @@
       <c r="A336" t="n">
         <v>1</v>
       </c>
-      <c r="B336" t="inlineStr">
+      <c r="B336" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18639,7 +19663,7 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J336" t="n">
@@ -18655,7 +19679,7 @@
       <c r="A337" t="n">
         <v>1</v>
       </c>
-      <c r="B337" t="inlineStr">
+      <c r="B337" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18704,7 +19728,7 @@
       <c r="A338" t="n">
         <v>1</v>
       </c>
-      <c r="B338" t="inlineStr">
+      <c r="B338" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18741,7 +19765,7 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J338" t="n">
@@ -18757,7 +19781,7 @@
       <c r="A339" t="n">
         <v>1</v>
       </c>
-      <c r="B339" t="inlineStr">
+      <c r="B339" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18806,7 +19830,7 @@
       <c r="A340" t="n">
         <v>1</v>
       </c>
-      <c r="B340" t="inlineStr">
+      <c r="B340" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18855,7 +19879,7 @@
       <c r="A341" t="n">
         <v>1</v>
       </c>
-      <c r="B341" t="inlineStr">
+      <c r="B341" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18892,7 +19916,7 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J341" t="n">
@@ -18908,7 +19932,7 @@
       <c r="A342" t="n">
         <v>1</v>
       </c>
-      <c r="B342" t="inlineStr">
+      <c r="B342" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -18945,7 +19969,7 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>ΥΠΕΡΩΡΙΑ</t>
+          <t>ΝΑΙ</t>
         </is>
       </c>
       <c r="J342" t="n">
@@ -18968,17 +19992,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -19003,15 +20018,10 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Ημέρες με Υπερωρία</t>
+          <t>Σύνολο Υπερωρίας Λεπτά</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
-        <is>
-          <t>Σύνολο Υπερωρίας Λεπτά</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>Σύνολο Υπερωρίας (HH:MM)</t>
         </is>
@@ -19021,7 +20031,7 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>047987630</t>
         </is>
@@ -19037,12 +20047,9 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F2" t="n">
         <v>23</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>00:23</t>
         </is>
@@ -19052,7 +20059,7 @@
       <c r="A3" t="n">
         <v>0</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>062233490</t>
         </is>
@@ -19068,12 +20075,9 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F3" t="n">
         <v>26</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>00:26</t>
         </is>
@@ -19083,7 +20087,7 @@
       <c r="A4" t="n">
         <v>0</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>141882270</t>
         </is>
@@ -19099,12 +20103,9 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F4" t="n">
         <v>24</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>00:24</t>
         </is>
@@ -19114,7 +20115,7 @@
       <c r="A5" t="n">
         <v>0</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>157123604</t>
         </is>
@@ -19130,12 +20131,9 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" t="n">
         <v>23</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>00:23</t>
         </is>
@@ -19145,7 +20143,7 @@
       <c r="A6" t="n">
         <v>0</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>160061762</t>
         </is>
@@ -19161,12 +20159,9 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" t="n">
         <v>24</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>00:24</t>
         </is>
@@ -19176,7 +20171,7 @@
       <c r="A7" t="n">
         <v>0</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>179124894</t>
         </is>
@@ -19192,12 +20187,9 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" t="n">
         <v>24</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>00:24</t>
         </is>
@@ -19207,7 +20199,7 @@
       <c r="A8" t="n">
         <v>1</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>036497310</t>
         </is>
@@ -19223,12 +20215,9 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" t="n">
         <v>15</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>00:15</t>
         </is>
@@ -19238,7 +20227,7 @@
       <c r="A9" t="n">
         <v>1</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>037843072</t>
         </is>
@@ -19254,12 +20243,9 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" t="n">
         <v>9</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>00:09</t>
         </is>
@@ -19269,7 +20255,7 @@
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>059365437</t>
         </is>
@@ -19285,12 +20271,9 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
-      </c>
-      <c r="F10" t="n">
         <v>16</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>00:16</t>
         </is>
@@ -19300,7 +20283,7 @@
       <c r="A11" t="n">
         <v>1</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>065510428</t>
         </is>
@@ -19316,12 +20299,9 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" t="n">
         <v>9</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>00:09</t>
         </is>
@@ -19331,7 +20311,7 @@
       <c r="A12" t="n">
         <v>1</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>068651452</t>
         </is>
@@ -19347,12 +20327,9 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" t="n">
         <v>10</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>00:10</t>
         </is>
@@ -19362,7 +20339,7 @@
       <c r="A13" t="n">
         <v>1</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>127063376</t>
         </is>
@@ -19378,12 +20355,9 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
-      </c>
-      <c r="F13" t="n">
         <v>12</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>00:12</t>
         </is>
@@ -19393,7 +20367,7 @@
       <c r="A14" t="n">
         <v>1</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>141897793</t>
         </is>
@@ -19409,12 +20383,9 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" t="n">
         <v>4</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>00:04</t>
         </is>
@@ -19424,7 +20395,7 @@
       <c r="A15" t="n">
         <v>1</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>156806706</t>
         </is>
@@ -19440,12 +20411,9 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>11</v>
-      </c>
-      <c r="F15" t="n">
         <v>16</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>00:16</t>
         </is>
@@ -19455,7 +20423,7 @@
       <c r="A16" t="n">
         <v>1</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>156822595</t>
         </is>
@@ -19471,12 +20439,9 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13</v>
-      </c>
-      <c r="F16" t="n">
         <v>20</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>00:20</t>
         </is>
@@ -19486,7 +20451,7 @@
       <c r="A17" t="n">
         <v>1</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>157133714</t>
         </is>
@@ -19502,12 +20467,9 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
-      </c>
-      <c r="F17" t="n">
         <v>14</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>00:14</t>
         </is>
@@ -19517,7 +20479,7 @@
       <c r="A18" t="n">
         <v>1</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>160088100</t>
         </is>
@@ -19535,10 +20497,7 @@
       <c r="E18" t="n">
         <v>3</v>
       </c>
-      <c r="F18" t="n">
-        <v>3</v>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>00:03</t>
         </is>
@@ -19548,7 +20507,7 @@
       <c r="A19" t="n">
         <v>1</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>170907466</t>
         </is>
@@ -19566,10 +20525,7 @@
       <c r="E19" t="n">
         <v>3</v>
       </c>
-      <c r="F19" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>00:03</t>
         </is>
@@ -19579,7 +20535,7 @@
       <c r="A20" t="n">
         <v>1</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>180453994</t>
         </is>
@@ -19595,15 +20551,1284 @@
         </is>
       </c>
       <c r="E20" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>00:16</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ΑΑ Παραρτηματος</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ΑΦΜ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Επώνυμο</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Όνομα</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Ημερομηνία Πρόσληψης</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Ημερομηνία Αποχώρησης</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Δικαιούμενη Κανονική Άδεια Προηγούμενου Έτους</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Υπόλοιπο Προηγούμενου Έτους</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Δικαιούμενη Κανονική Άδεια Τρέχοντος Έτους</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Κανονική Άδεια από Προηγούμενο Έτος</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Κανονική Άδεια από Τρέχον Έτος</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Σύνολο Κανονικής Άδειας</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Σύνολο Ασθενείας</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Σύνολο Άνευ Αποδοχών</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Υπόλοιπο Προηγούμενου Έτους Μετά</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Υπόλοιπο Τρέχοντος Έτους Μετά</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>047987630</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ΣΤΑΜΑΤΟΠΟΥΛΟΣ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ΝΙΚΟΛΑΟΣ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>11/09/2013</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>062233490</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ΝΙΦΟΡΑΣ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ΔΗΜΗΤΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>02/05/2018</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>31</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>26</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>141882270</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ΔΙΔΑΧΟΣ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>01/07/2016</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>157123604</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ΒΛΑΧΟΣ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ΠΕΤΡΟΣ</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23/04/2018</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>22</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>160061762</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ΜΑΡΑΓΚΟΥ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ΒΙΡΓΙΝΙΑ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>07/10/2024</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>22</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>167218780</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ΔΗΜΗΤΡΟΠΟΥΛΟΣ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ ΠΑΝΑΓΙΩΤΗΣ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>05/07/2022</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>26</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>22</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>19</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>179124894</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ΚΑΤΣΑΙΤΗΣ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ΓΕΡΑΣΙΜΟΣ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>01/07/2024</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>26</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>22</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>036497310</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ΑΘΑΝΑΣΟΠΟΥΛΟΣ</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ΣΤΑΥΡΟΣ</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20/10/2015</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>31</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="n">
+        <v>26</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>18</v>
+      </c>
+      <c r="P9" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>037843072</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ΒΑΒΑΡΟΥΤΑ</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ΚΩΝΣΤΑΝΤΙΝΑ</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>29/10/2003</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>25</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>25</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>059365437</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ΚΑΤΣΑΙΤΗΣ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ΣΤΑΥΡΟΣ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>01/03/1995</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>31</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>26</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>065510428</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ΛΟΥΚΙΔΗ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ΣΤΕΛΛΑ</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>02/10/2000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>068651452</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΟΠΟΥΛΟΥ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ΜΑΡΙΑ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>25</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>127063376</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ΞΟΥΛΟΣ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>13/11/2002</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>25</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>141897793</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ΔΙΔΑΧΟΥ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ΑΦΡΟΔΙΤΗ</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>156806706</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ΔΙΔΑΧΟΣ</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ΠΑΝΑΓΙΩΤΗΣ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>01/07/2019</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>26</v>
+      </c>
+      <c r="H16" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" t="n">
+        <v>22</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>11</v>
+      </c>
+      <c r="P16" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>156822595</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ΔΙΔΑΧΟΣ</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ΧΡΗΣΤΟΣ</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>04/03/2020</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>26</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>22</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>157133714</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ΚΑΝΕΛΛΑΚΗΣ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ΚΩΝΣΤΑΝΤΙΝΟΣ</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>07/04/2021</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>26</v>
+      </c>
+      <c r="H18" t="n">
+        <v>14</v>
+      </c>
+      <c r="I18" t="n">
+        <v>22</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>12</v>
       </c>
-      <c r="F20" t="n">
-        <v>16</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>00:16</t>
-        </is>
+      <c r="P18" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>160088100</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ΔΙΔΑΧΟΣ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ΠΑΝΑΓΙΩΤΗΣ</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>01/09/2022</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" t="n">
+        <v>19</v>
+      </c>
+      <c r="I19" t="n">
+        <v>22</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>18</v>
+      </c>
+      <c r="P19" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>170907466</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ΔΙΔΑΧΟΣ</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>17/01/2024</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>26</v>
+      </c>
+      <c r="H20" t="n">
+        <v>14</v>
+      </c>
+      <c r="I20" t="n">
+        <v>22</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>8</v>
+      </c>
+      <c r="P20" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>174736295</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ΑΝΤΥΠΑΣ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ΣΩΤΗΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>02/07/2024</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>25</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>22</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>19</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>180453994</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ΚΥΡΙΑΖΗΣ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ΜΙΧΑΗΛ</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>22/08/2025</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>25</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" t="n">
+        <v>21</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>12</v>
+      </c>
+      <c r="P22" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
